--- a/outputs/evaluation/architecture/validation/CF_M06/run_1/CF_M06_arch_eval_by_type.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M06/run_1/CF_M06_arch_eval_by_type.xlsx
@@ -524,13 +524,13 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -580,22 +580,22 @@
         <v>7</v>
       </c>
       <c r="C6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D6" t="n">
         <v>4</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>0.6667</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2857</v>
+        <v>0.5714</v>
       </c>
     </row>
     <row r="7">
@@ -608,22 +608,22 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8571</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8">
@@ -636,21 +636,19 @@
         <v>3</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G8" t="n">
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -669,19 +667,19 @@
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
